--- a/AAII_Financials/Quarterly/XYIGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XYIGY_QTR_FIN.xlsx
@@ -3829,10 +3829,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>59200</v>
+        <v>56300</v>
       </c>
       <c r="E83" s="3">
-        <v>61600</v>
+        <v>58600</v>
       </c>
       <c r="F83" s="3">
         <v>43000</v>
